--- a/output/pdf_financials_xlsx/GWO.xlsx
+++ b/output/pdf_financials_xlsx/GWO.xlsx
@@ -1237,10 +1237,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-124</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-115</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -1793,10 +1793,8 @@
       <c r="J34" s="3" t="n">
         <v>10709</v>
       </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K34" s="3" t="n">
+        <v>8902</v>
       </c>
     </row>
     <row r="35">
@@ -1832,10 +1830,8 @@
       <c r="J35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1871,10 +1867,8 @@
       <c r="J36" s="3" t="n">
         <v>10709</v>
       </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K36" s="3" t="n">
+        <v>8902</v>
       </c>
     </row>
     <row r="37">
@@ -1910,10 +1904,8 @@
       <c r="J37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1949,10 +1941,8 @@
       <c r="J38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1988,10 +1978,8 @@
       <c r="J39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2027,10 +2015,8 @@
       <c r="J40" s="3" t="n">
         <v>5402</v>
       </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K40" s="3" t="n">
+        <v>6029</v>
       </c>
     </row>
     <row r="41">
@@ -2066,10 +2052,8 @@
       <c r="J41" s="3" t="n">
         <v>5402</v>
       </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K41" s="3" t="n">
+        <v>6029</v>
       </c>
     </row>
     <row r="42">
@@ -2105,10 +2089,8 @@
       <c r="J42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2144,10 +2126,8 @@
       <c r="J43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2183,10 +2163,8 @@
       <c r="J44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2222,10 +2200,8 @@
       <c r="J45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2261,10 +2237,8 @@
       <c r="J46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2300,10 +2274,8 @@
       <c r="J47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2339,10 +2311,8 @@
       <c r="J48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2435,10 +2405,8 @@
       <c r="J50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2474,10 +2442,8 @@
       <c r="J51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2513,10 +2479,8 @@
       <c r="J52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2552,10 +2516,8 @@
       <c r="J53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2591,10 +2553,8 @@
       <c r="J54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2687,10 +2647,8 @@
       <c r="J56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2726,10 +2684,8 @@
       <c r="J57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2765,10 +2721,8 @@
       <c r="J58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2804,10 +2758,8 @@
       <c r="J59" s="3" t="n">
         <v>4958</v>
       </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K59" s="3" t="n">
+        <v>4912</v>
       </c>
     </row>
     <row r="60">
@@ -2843,10 +2795,8 @@
       <c r="J60" s="3" t="n">
         <v>11428</v>
       </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K60" s="3" t="n">
+        <v>11283</v>
       </c>
     </row>
     <row r="61">
@@ -2882,10 +2832,8 @@
       <c r="J61" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2978,10 +2926,8 @@
       <c r="J63" s="3" t="n">
         <v>243785</v>
       </c>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K63" s="3" t="n">
+        <v>250051</v>
       </c>
     </row>
     <row r="64">
@@ -3017,10 +2963,8 @@
       <c r="J64" s="3" t="n">
         <v>3524</v>
       </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K64" s="3" t="n">
+        <v>3981</v>
       </c>
     </row>
     <row r="65">
@@ -3056,10 +3000,8 @@
       <c r="J65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3095,10 +3037,8 @@
       <c r="J66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3134,10 +3074,8 @@
       <c r="J67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3173,10 +3111,8 @@
       <c r="J68" s="3" t="n">
         <v>3524</v>
       </c>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K68" s="3" t="n">
+        <v>3981</v>
       </c>
     </row>
     <row r="69">
@@ -3212,10 +3148,8 @@
       <c r="J69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3251,10 +3185,8 @@
       <c r="J70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3290,10 +3222,8 @@
       <c r="J71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3329,10 +3259,8 @@
       <c r="J72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3368,10 +3296,8 @@
       <c r="J73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3407,10 +3333,8 @@
       <c r="J74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3446,10 +3370,8 @@
       <c r="J75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3542,10 +3464,8 @@
       <c r="J77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3581,10 +3501,8 @@
       <c r="J78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3620,10 +3538,8 @@
       <c r="J79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -3716,10 +3632,8 @@
       <c r="J81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3755,10 +3669,8 @@
       <c r="J82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3794,10 +3706,8 @@
       <c r="J83" s="3" t="n">
         <v>834</v>
       </c>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K83" s="3" t="n">
+        <v>937</v>
       </c>
     </row>
     <row r="84">
@@ -3833,10 +3743,8 @@
       <c r="J84" s="3" t="n">
         <v>834</v>
       </c>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K84" s="3" t="n">
+        <v>937</v>
       </c>
     </row>
     <row r="85">
@@ -3872,10 +3780,8 @@
       <c r="J85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3968,10 +3874,8 @@
       <c r="J87" s="3" t="n">
         <v>769509</v>
       </c>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K87" s="3" t="n">
+        <v>829825</v>
       </c>
     </row>
     <row r="88">
@@ -4007,10 +3911,8 @@
       <c r="J88" s="3" t="n">
         <v>6071</v>
       </c>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K88" s="3" t="n">
+        <v>5983</v>
       </c>
     </row>
     <row r="89">
@@ -4046,10 +3948,8 @@
       <c r="J89" s="3" t="n">
         <v>2720</v>
       </c>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K89" s="3" t="n">
+        <v>2920</v>
       </c>
     </row>
     <row r="90">
@@ -4142,10 +4042,8 @@
       <c r="J91" s="3" t="n">
         <v>1776</v>
       </c>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K91" s="3" t="n">
+        <v>1742</v>
       </c>
     </row>
     <row r="92">
@@ -4181,10 +4079,8 @@
       <c r="J92" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K92" s="3" t="n">
+        <v>209</v>
       </c>
     </row>
     <row r="93">
@@ -4220,10 +4116,8 @@
       <c r="J93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4259,10 +4153,8 @@
       <c r="J94" s="3" t="n">
         <v>32654</v>
       </c>
-      <c r="K94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K94" s="3" t="n">
+        <v>33003</v>
       </c>
     </row>
     <row r="95">
@@ -4298,10 +4190,8 @@
       <c r="J95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4337,10 +4227,8 @@
       <c r="J96" s="3" t="n">
         <v>32654</v>
       </c>
-      <c r="K96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K96" s="3" t="n">
+        <v>33003</v>
       </c>
     </row>
     <row r="97">
@@ -4376,10 +4264,8 @@
       <c r="J97" s="3" t="n">
         <v>0.1339458949484177</v>
       </c>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K97" s="3" t="n">
+        <v>0.1319850750446909</v>
       </c>
     </row>
     <row r="98">
@@ -5924,10 +5810,8 @@
       <c r="M2" s="5" t="n">
         <v>10709</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N2" s="5" t="n">
+        <v>8902</v>
       </c>
     </row>
     <row r="3">
@@ -5980,10 +5864,8 @@
       <c r="M3" s="5" t="n">
         <v>167114</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N3" s="5" t="n">
+        <v>174468</v>
       </c>
     </row>
     <row r="4">
@@ -6040,10 +5922,8 @@
       <c r="M4" s="5" t="n">
         <v>38879</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N4" s="5" t="n">
+        <v>36873</v>
       </c>
     </row>
     <row r="5">
@@ -6096,10 +5976,8 @@
       <c r="M5" s="5" t="n">
         <v>18826</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N5" s="5" t="n">
+        <v>21515</v>
       </c>
     </row>
     <row r="6">
@@ -6152,10 +6030,8 @@
       <c r="M6" s="5" t="n">
         <v>8257</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N6" s="5" t="n">
+        <v>8293</v>
       </c>
     </row>
     <row r="7">
@@ -6208,10 +6084,8 @@
       <c r="M7" s="5" t="n">
         <v>243785</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N7" s="5" t="n">
+        <v>250051</v>
       </c>
     </row>
     <row r="8">
@@ -6272,10 +6146,8 @@
       <c r="M8" s="5" t="n">
         <v>1193</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N8" s="5" t="n">
+        <v>1571</v>
       </c>
     </row>
     <row r="9">
@@ -6336,10 +6208,8 @@
       <c r="M9" s="5" t="n">
         <v>17842</v>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N9" s="5" t="n">
+        <v>16850</v>
       </c>
     </row>
     <row r="10">
@@ -6355,12 +6225,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Assets held for sale</t>
+          <t>Goodwill (note 9)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AssetsHeldForSale</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -6399,17 +6269,13 @@
         </is>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4467</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11249</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>11428</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>11283</v>
       </c>
     </row>
     <row r="11">
@@ -6425,12 +6291,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Goodwill (note 9)</t>
+          <t>Intangible assets (note 9)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>OtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6469,15 +6335,13 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>11249</v>
+        <v>4484</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>11428</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4958</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>4912</v>
       </c>
     </row>
     <row r="12">
@@ -6493,23 +6357,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Intangible assets (note 9)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>OtherIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Derivative financial instruments (note 30)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>652</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>461</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -6537,15 +6393,13 @@
         </is>
       </c>
       <c r="L12" s="5" t="n">
-        <v>4484</v>
+        <v>2219</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>4958</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2431</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>1863</v>
       </c>
     </row>
     <row r="13">
@@ -6561,15 +6415,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Derivative financial instruments (note 30)</t>
+          <t>Owner occupied properties (note 10)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" s="5" t="n">
-        <v>652</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>461</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -6597,15 +6455,13 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>2219</v>
+        <v>731</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>2431</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>789</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>829</v>
       </c>
     </row>
     <row r="14">
@@ -6621,7 +6477,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Owner occupied properties (note 10)</t>
+          <t>Fixed assets (note 10)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -6661,15 +6517,13 @@
         </is>
       </c>
       <c r="L14" s="5" t="n">
-        <v>731</v>
+        <v>335</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>789</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>346</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>395</v>
       </c>
     </row>
     <row r="15">
@@ -6685,10 +6539,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fixed assets (note 10)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Accounts and interest receivable</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -6725,15 +6583,13 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>335</v>
+        <v>4863</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>346</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5402</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>6029</v>
       </c>
     </row>
     <row r="16">
@@ -6749,12 +6605,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Accounts and interest receivable</t>
+          <t>Other assets (note 11)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>OtherAssets</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6793,15 +6649,13 @@
         </is>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4863</v>
+        <v>14483</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>5402</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15265</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>15190</v>
       </c>
     </row>
     <row r="17">
@@ -6817,14 +6671,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other assets (note 11)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>OtherAssets</t>
-        </is>
-      </c>
+          <t>Current income taxes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -6840,36 +6690,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H17" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>336</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>14483</v>
+        <v>260</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>15265</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>272</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>401</v>
       </c>
     </row>
     <row r="18">
@@ -6885,10 +6725,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Current income taxes</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Deferred tax assets (note 29)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DeferredTaxAssets</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -6904,28 +6748,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n">
-        <v>134</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>218</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>268</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>336</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L18" s="5" t="n">
-        <v>260</v>
+        <v>1848</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>272</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2066</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>2285</v>
       </c>
     </row>
     <row r="19">
@@ -6941,14 +6791,10 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Deferred tax assets (note 29)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>DeferredTaxAssets</t>
-        </is>
-      </c>
+          <t>Investments on account of segregated fund policyholders (note 17)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -6985,15 +6831,13 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1848</v>
+        <v>422956</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>2066</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>496386</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>551169</v>
       </c>
     </row>
     <row r="20">
@@ -7009,55 +6853,45 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Investments on account of segregated fund policyholders (note 17)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total assets $</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>356709</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>399935</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H20" s="5" t="n">
+        <v>419838</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>427689</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>630488</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>701455</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>422956</v>
+        <v>713230</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>496386</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>802163</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>862828</v>
       </c>
     </row>
     <row r="21">
@@ -7066,26 +6900,22 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>assets</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Total assets $</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>356709</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>399935</v>
+          <t>Insurance contract liabilities (note 14) $</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -7093,27 +6923,29 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>419838</v>
+        <v>159524</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>427689</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>630488</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>701455</v>
+        <v>166720</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>713230</v>
+        <v>144388</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>802163</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>155683</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>161644</v>
       </c>
     </row>
     <row r="22">
@@ -7125,7 +6957,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Insurance contract liabilities (note 14) $</t>
+          <t>Investment contract liabilities (note 16)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -7144,11 +6976,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n">
-        <v>159524</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>166720</v>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -7161,15 +6997,13 @@
         </is>
       </c>
       <c r="L22" s="5" t="n">
-        <v>144388</v>
+        <v>88919</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>155683</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>90157</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>89042</v>
       </c>
     </row>
     <row r="23">
@@ -7181,7 +7015,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Investment contract liabilities (note 16)</t>
+          <t>Reinsurance contract held liabilities (note 15)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -7221,15 +7055,13 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>88919</v>
+        <v>648</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>90157</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>795</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>919</v>
       </c>
     </row>
     <row r="24">
@@ -7241,7 +7073,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reinsurance contract held liabilities (note 15)</t>
+          <t>Debentures and other debt instruments (note 18)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -7281,15 +7113,13 @@
         </is>
       </c>
       <c r="L24" s="5" t="n">
-        <v>648</v>
+        <v>9046</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>795</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9469</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>8792</v>
       </c>
     </row>
     <row r="25">
@@ -7301,29 +7131,21 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Liabilities held for sale</t>
+          <t>Derivative financial instruments (note 30)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="5" t="n">
+        <v>1195</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>2624</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>2.012</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>1.336</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -7341,17 +7163,13 @@
         </is>
       </c>
       <c r="L25" s="5" t="n">
-        <v>2407</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1288</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>2137</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>2412</v>
       </c>
     </row>
     <row r="26">
@@ -7363,55 +7181,43 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Debentures and other debt instruments (note 18)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AccountsPayable</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>2.049</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>2684</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>3262</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>3032</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>3194</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>9046</v>
+        <v>3216</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>9469</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3524</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>3981</v>
       </c>
     </row>
     <row r="27">
@@ -7423,21 +7229,33 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Derivative financial instruments (note 30)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" s="5" t="n">
-        <v>1195</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>2624</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>2.012</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>1.336</v>
+          <t>Other liabilities (note 20)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OtherLiabilities</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -7455,15 +7273,13 @@
         </is>
       </c>
       <c r="L27" s="5" t="n">
-        <v>1288</v>
+        <v>9587</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>2137</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10230</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>10431</v>
       </c>
     </row>
     <row r="28">
@@ -7475,45 +7291,41 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>AccountsPayable</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>1480</v>
+          <t>Current income taxes</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1755</v>
+        <v>492</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>2.049</v>
+        <v>0.494</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>2684</v>
+        <v>464</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>3262</v>
+        <v>402</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>3032</v>
+        <v>193</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>3194</v>
+        <v>150</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>3216</v>
+        <v>137</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>3524</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>294</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>498</v>
       </c>
     </row>
     <row r="29">
@@ -7525,12 +7337,12 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Other liabilities (note 20)</t>
+          <t>Deferred tax liabilities (note 29)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OtherLiabilities</t>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -7569,15 +7381,13 @@
         </is>
       </c>
       <c r="L29" s="5" t="n">
-        <v>9587</v>
+        <v>787</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>10230</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>834</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>937</v>
       </c>
     </row>
     <row r="30">
@@ -7589,7 +7399,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Current income taxes</t>
+          <t>Insurance contracts on account of segregated fund policyholders (note 17)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -7598,34 +7408,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n">
-        <v>492</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>464</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>402</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>193</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>150</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L30" s="5" t="n">
-        <v>137</v>
+        <v>60302</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>294</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>66343</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>70418</v>
       </c>
     </row>
     <row r="31">
@@ -7637,14 +7457,10 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deferred tax liabilities (note 29)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NonCurrentDeferredTaxesLiabilities</t>
-        </is>
-      </c>
+          <t>Investment contracts on account of segregated fund policyholders (note 17)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -7681,15 +7497,13 @@
         </is>
       </c>
       <c r="L31" s="5" t="n">
-        <v>787</v>
+        <v>362654</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>834</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>430043</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>480751</v>
       </c>
     </row>
     <row r="32">
@@ -7701,55 +7515,43 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Insurance contracts on account of segregated fund policyholders (note 17)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>334812</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>374675</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>374.725</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>394302</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>400291</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>600005</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>669137</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>60302</v>
+        <v>683379</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>66343</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>769509</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>829825</v>
       </c>
     </row>
     <row r="33">
@@ -7758,58 +7560,46 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Investment contracts on account of segregated fund policyholders (note 17)</t>
+          <t>Participating account surplus in subsidiaries</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E33" s="5" t="n">
+        <v>2480</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>2626</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>2.782</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>2771</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>2737</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>3138</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>3156</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>362654</v>
+        <v>2847</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>430043</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3041</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>3079</v>
       </c>
     </row>
     <row r="34">
@@ -7818,48 +7608,46 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
+          <t>Non-controlling interests in subsidiaries</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
-        <v>334812</v>
+        <v>163</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>374675</v>
+        <v>195</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>374.725</v>
+        <v>0.224</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>394302</v>
+        <v>164</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>400291</v>
+        <v>138</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>600005</v>
+        <v>129</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>669137</v>
+        <v>152</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>683379</v>
+        <v>168</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>769509</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>72</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="35">
@@ -7870,46 +7658,54 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Participating account surplus in subsidiaries</t>
+          <t>Limited recourse capital notes</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" s="5" t="n">
-        <v>2480</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>2626</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>2.782</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>2771</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>2737</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="5" t="n">
-        <v>3138</v>
+        <v>1500</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>3156</v>
+        <v>1500</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>2847</v>
+        <v>1500</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>3041</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1500</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="36">
@@ -7920,46 +7716,48 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Non-controlling interests in subsidiaries</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Preferred shares</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PreferredStock</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
-        <v>163</v>
+        <v>2514</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>195</v>
+        <v>2514</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.224</v>
+        <v>2.514</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>164</v>
+        <v>2714</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>138</v>
+        <v>2714</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>129</v>
+        <v>2720</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>152</v>
+        <v>2720</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>168</v>
+        <v>2720</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2720</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>2920</v>
       </c>
     </row>
     <row r="37">
@@ -7975,51 +7773,43 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Limited recourse capital notes</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Common shares</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CommonStock</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>7102</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>7156</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>7260</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>7283</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>1500</v>
+        <v>5748</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>1500</v>
+        <v>5791</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6071</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>5983</v>
       </c>
     </row>
     <row r="38">
@@ -8035,45 +7825,39 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Preferred shares</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>PreferredStock</t>
-        </is>
-      </c>
+          <t>Accumulated surplus</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>2514</v>
+        <v>9134</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>2514</v>
+        <v>10416</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>2.514</v>
+        <v>11.465</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>2714</v>
+        <v>12098</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>2714</v>
+        <v>13342</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>2720</v>
+        <v>16424</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>2720</v>
+        <v>17809</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>2720</v>
+        <v>15492</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>2720</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>17266</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>17503</v>
       </c>
     </row>
     <row r="39">
@@ -8089,45 +7873,57 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Common shares</t>
+          <t>Accumulated other comprehensive income (note 27)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CommonStock</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>7102</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>7156</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>7260</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>7283</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>5748</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>5791</v>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L39" s="5" t="n">
-        <v>6000</v>
+        <v>890</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>6071</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1776</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>1742</v>
       </c>
     </row>
     <row r="40">
@@ -8143,41 +7939,43 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Accumulated surplus</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Contributed surplus</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>9134</v>
+        <v>126</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>10416</v>
+        <v>135</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>11.465</v>
+        <v>0.147</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>12098</v>
+        <v>143</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>13342</v>
+        <v>139</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>16424</v>
+        <v>192</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>17809</v>
+        <v>209</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>15492</v>
+        <v>234</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>17266</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>208</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>209</v>
       </c>
     </row>
     <row r="41">
@@ -8193,59 +7991,43 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Accumulated other comprehensive income (note 27)</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GainsLossesNotAffectingRetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>21897</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>25260</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>25.008</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>25536</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>27398</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>30483</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>32318</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>890</v>
+        <v>29851</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>1776</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>32654</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>33003</v>
       </c>
     </row>
     <row r="42">
@@ -8261,45 +8043,43 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Total liabilities and equity $</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>126</v>
+        <v>356709</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>135</v>
+        <v>399935</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.147</v>
+        <v>399.733</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>143</v>
+        <v>419838</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>139</v>
+        <v>427689</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>192</v>
+        <v>630488</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>209</v>
+        <v>701455</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>234</v>
+        <v>713230</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>208</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>802163</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>862828</v>
       </c>
     </row>
     <row r="43">
@@ -8310,45 +8090,61 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>assets</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Total equity</t>
+          <t>Assets held for sale</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>21897</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>25260</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>25.008</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>25536</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>27398</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>30483</v>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>32318</v>
+          <t>AssetsHeldForSale</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L43" s="5" t="n">
-        <v>29851</v>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v>32654</v>
+        <v>4467</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -8362,47 +8158,55 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Total liabilities and equity $</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>356709</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>399935</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>399.733</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>419838</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>427689</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>630488</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>701455</v>
+          <t>Liabilities held for sale</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L44" s="5" t="n">
-        <v>713230</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>802163</v>
+        <v>2407</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -24974,7 +24778,11 @@
           <t>Net loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
